--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N22_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>4.293091733455625</v>
       </c>
       <c r="E2" t="n">
-        <v>1.894500372595287</v>
+        <v>4.025993709671311</v>
       </c>
       <c r="F2" t="n">
-        <v>1.707884384371042</v>
+        <v>4.023317110799607</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.000389485238492</v>
+        <v>12.2989898082791</v>
       </c>
       <c r="D3" t="n">
-        <v>5.797799383938861</v>
+        <v>12.55942246500859</v>
       </c>
       <c r="E3" t="n">
-        <v>1.894500372595287</v>
+        <v>4.025993709671311</v>
       </c>
       <c r="F3" t="n">
-        <v>1.707884384371042</v>
+        <v>4.023317110799607</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,23 +544,55 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>6.000389485238492</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.797799383938861</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.025993709671311</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.023317110799607</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0029F0001T0006Z000C1N22.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>1.378217442206272</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>1.664942344435208</v>
       </c>
-      <c r="E4" t="n">
-        <v>1.894500372595287</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.707884384371042</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>4.025993709671311</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.023317110799607</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>T7604</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.046706151730008</v>
+        <v>0.6575897496561263</v>
       </c>
       <c r="D2" t="n">
-        <v>4.293091733455625</v>
+        <v>0.697627406686539</v>
       </c>
       <c r="E2" t="n">
-        <v>4.025993709671311</v>
+        <v>0.654223977821588</v>
       </c>
       <c r="F2" t="n">
-        <v>4.023317110799607</v>
+        <v>0.6537890305049362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.2989898082791</v>
+        <v>1.998585843845353</v>
       </c>
       <c r="D3" t="n">
-        <v>12.55942246500859</v>
+        <v>2.040906150563896</v>
       </c>
       <c r="E3" t="n">
-        <v>4.025993709671311</v>
+        <v>0.654223977821588</v>
       </c>
       <c r="F3" t="n">
-        <v>4.023317110799607</v>
+        <v>0.6537890305049362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.000389485238492</v>
+        <v>0.975063291351255</v>
       </c>
       <c r="D4" t="n">
-        <v>5.797799383938861</v>
+        <v>0.9421423998900649</v>
       </c>
       <c r="E4" t="n">
-        <v>4.025993709671311</v>
+        <v>0.654223977821588</v>
       </c>
       <c r="F4" t="n">
-        <v>4.023317110799607</v>
+        <v>0.6537890305049362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.378217442206272</v>
+        <v>0.2239603343585191</v>
       </c>
       <c r="D5" t="n">
-        <v>1.664942344435208</v>
+        <v>0.2705531309707213</v>
       </c>
       <c r="E5" t="n">
-        <v>4.025993709671311</v>
+        <v>0.654223977821588</v>
       </c>
       <c r="F5" t="n">
-        <v>4.023317110799607</v>
+        <v>0.6537890305049362</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
